--- a/erp-server/erp-server-file/src/main/resources/excel/scm/purchaseOrderExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/scm/purchaseOrderExport.xlsx
@@ -152,7 +152,7 @@
     <t>{.deliveryWarehouseName}</t>
   </si>
   <si>
-    <t>{.taxPriceName}</t>
+    <t>{.taxPrice}</t>
   </si>
   <si>
     <t>{.taxRateStr}</t>
@@ -161,7 +161,7 @@
     <t>{.purchaseQty}</t>
   </si>
   <si>
-    <t>{.purchaseAmountName}</t>
+    <t>{.purchaseAmount}</t>
   </si>
   <si>
     <t>{.deliveryQty}</t>

--- a/erp-server/erp-server-file/src/main/resources/excel/scm/purchaseOrderExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/scm/purchaseOrderExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="采购订单数据" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t>采购单号</t>
   </si>
@@ -38,6 +38,9 @@
     <t>单据类型</t>
   </si>
   <si>
+    <t>退货方式</t>
+  </si>
+  <si>
     <t>供应商</t>
   </si>
   <si>
@@ -120,6 +123,9 @@
   </si>
   <si>
     <t>{.typeName}</t>
+  </si>
+  <si>
+    <t>{.returnTypeName}</t>
   </si>
   <si>
     <t>{.supplierName}</t>
@@ -1397,25 +1403,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AB2"/>
+  <dimension ref="A1:AC2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
     <col min="2" max="2" width="15.75" customWidth="1"/>
-    <col min="3" max="3" width="12.625" customWidth="1"/>
-    <col min="4" max="4" width="12.375" customWidth="1"/>
-    <col min="5" max="5" width="14.75" customWidth="1"/>
-    <col min="6" max="6" width="15.75" customWidth="1"/>
-    <col min="7" max="7" width="13.5" customWidth="1"/>
-    <col min="9" max="9" width="17" customWidth="1"/>
-    <col min="12" max="12" width="14.5" customWidth="1"/>
-    <col min="13" max="13" width="15.875" customWidth="1"/>
-    <col min="24" max="24" width="14" customWidth="1"/>
-    <col min="25" max="25" width="22.125" customWidth="1"/>
-    <col min="28" max="28" width="20" customWidth="1"/>
+    <col min="3" max="4" width="12.625" customWidth="1"/>
+    <col min="5" max="5" width="12.375" customWidth="1"/>
+    <col min="6" max="6" width="14.75" customWidth="1"/>
+    <col min="7" max="7" width="15.75" customWidth="1"/>
+    <col min="8" max="8" width="13.5" customWidth="1"/>
+    <col min="10" max="10" width="17" customWidth="1"/>
+    <col min="13" max="13" width="14.5" customWidth="1"/>
+    <col min="14" max="14" width="15.875" customWidth="1"/>
+    <col min="25" max="25" width="14" customWidth="1"/>
+    <col min="26" max="26" width="22.125" customWidth="1"/>
+    <col min="29" max="29" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="18" customHeight="1" spans="1:28">
+    <row r="1" s="1" customFormat="1" ht="18" customHeight="1" spans="1:29">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1500,91 +1506,97 @@
       <c r="AB1" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="AC1" s="2" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="2" spans="1:28">
+    <row r="2" spans="1:29">
       <c r="A2" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="W2" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="X2" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Y2" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Z2" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AA2" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="AC2" s="3" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/scm/purchaseOrderExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/scm/purchaseOrderExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="采购订单数据" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
   <si>
     <t>采购单号</t>
   </si>
@@ -71,6 +71,9 @@
     <t>交货仓库</t>
   </si>
   <si>
+    <t>仓位</t>
+  </si>
+  <si>
     <t>含税单价</t>
   </si>
   <si>
@@ -95,6 +98,12 @@
     <t>退货数量</t>
   </si>
   <si>
+    <t>质检退货</t>
+  </si>
+  <si>
+    <t>库存退货</t>
+  </si>
+  <si>
     <t>备注</t>
   </si>
   <si>
@@ -158,6 +167,9 @@
     <t>{.deliveryWarehouseName}</t>
   </si>
   <si>
+    <t>{.warehouseLocation}</t>
+  </si>
+  <si>
     <t>{.taxPrice}</t>
   </si>
   <si>
@@ -180,6 +192,12 @@
   </si>
   <si>
     <t>{.returnQty}</t>
+  </si>
+  <si>
+    <t>{.qcReturnQty}</t>
+  </si>
+  <si>
+    <t>{.stockReturnQty}</t>
   </si>
   <si>
     <t>{.remark}</t>
@@ -1403,7 +1421,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AC2"/>
+  <dimension ref="A1:AF2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -1415,13 +1433,13 @@
     <col min="8" max="8" width="13.5" customWidth="1"/>
     <col min="10" max="10" width="17" customWidth="1"/>
     <col min="13" max="13" width="14.5" customWidth="1"/>
-    <col min="14" max="14" width="15.875" customWidth="1"/>
-    <col min="25" max="25" width="14" customWidth="1"/>
-    <col min="26" max="26" width="22.125" customWidth="1"/>
-    <col min="29" max="29" width="20" customWidth="1"/>
+    <col min="14" max="15" width="15.875" customWidth="1"/>
+    <col min="28" max="28" width="14" customWidth="1"/>
+    <col min="29" max="29" width="22.125" customWidth="1"/>
+    <col min="32" max="32" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="18" customHeight="1" spans="1:29">
+    <row r="1" s="1" customFormat="1" ht="18" customHeight="1" spans="1:32">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1509,94 +1527,112 @@
       <c r="AC1" s="2" t="s">
         <v>28</v>
       </c>
+      <c r="AD1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="2" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="2" spans="1:29">
+    <row r="2" spans="1:32">
       <c r="A2" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="W2" s="3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="X2" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Y2" s="3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="Z2" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="AA2" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="AC2" s="3" t="s">
-        <v>57</v>
+        <v>60</v>
+      </c>
+      <c r="AD2" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE2" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="AF2" s="3" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/scm/purchaseOrderExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/scm/purchaseOrderExport.xlsx
@@ -167,7 +167,7 @@
     <t>{.deliveryWarehouseName}</t>
   </si>
   <si>
-    <t>{.warehouseLocation}</t>
+    <t>{.warehouseLocationName}</t>
   </si>
   <si>
     <t>{.taxPrice}</t>

--- a/erp-server/erp-server-file/src/main/resources/excel/scm/purchaseOrderExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/scm/purchaseOrderExport.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="采购订单数据" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t>采购单号</t>
   </si>
@@ -125,6 +125,9 @@
     <t>创建时间</t>
   </si>
   <si>
+    <t>采购组织</t>
+  </si>
+  <si>
     <t>{.code}</t>
   </si>
   <si>
@@ -219,6 +222,9 @@
   </si>
   <si>
     <t>{.createTime}</t>
+  </si>
+  <si>
+    <t>{.purchaseOrgName}</t>
   </si>
 </sst>
 </file>
@@ -1421,7 +1427,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AF2"/>
+  <dimension ref="A1:AG2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -1439,7 +1445,7 @@
     <col min="32" max="32" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="18" customHeight="1" spans="1:32">
+    <row r="1" s="1" customFormat="1" ht="18" customHeight="1" spans="1:33">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1536,103 +1542,109 @@
       <c r="AF1" s="2" t="s">
         <v>31</v>
       </c>
+      <c r="AG1" s="2" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="2" spans="1:32">
+    <row r="2" spans="1:33">
       <c r="A2" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="W2" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="X2" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Y2" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Z2" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AA2" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AC2" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD2" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AE2" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AF2" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="AG2" s="3" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/scm/purchaseOrderExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/scm/purchaseOrderExport.xlsx
@@ -32,6 +32,9 @@
     <t>采购单号</t>
   </si>
   <si>
+    <t>采购组织</t>
+  </si>
+  <si>
     <t>来源单号</t>
   </si>
   <si>
@@ -125,12 +128,12 @@
     <t>创建时间</t>
   </si>
   <si>
-    <t>采购组织</t>
-  </si>
-  <si>
     <t>{.code}</t>
   </si>
   <si>
+    <t>{.purchaseOrgName}</t>
+  </si>
+  <si>
     <t>{.sourceCode}</t>
   </si>
   <si>
@@ -222,9 +225,6 @@
   </si>
   <si>
     <t>{.createTime}</t>
-  </si>
-  <si>
-    <t>{.purchaseOrgName}</t>
   </si>
 </sst>
 </file>
@@ -1431,18 +1431,19 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
-    <col min="2" max="2" width="15.75" customWidth="1"/>
-    <col min="3" max="4" width="12.625" customWidth="1"/>
-    <col min="5" max="5" width="12.375" customWidth="1"/>
-    <col min="6" max="6" width="14.75" customWidth="1"/>
-    <col min="7" max="7" width="15.75" customWidth="1"/>
-    <col min="8" max="8" width="13.5" customWidth="1"/>
-    <col min="10" max="10" width="17" customWidth="1"/>
-    <col min="13" max="13" width="14.5" customWidth="1"/>
-    <col min="14" max="15" width="15.875" customWidth="1"/>
-    <col min="28" max="28" width="14" customWidth="1"/>
-    <col min="29" max="29" width="22.125" customWidth="1"/>
-    <col min="32" max="32" width="20" customWidth="1"/>
+    <col min="2" max="2" width="16.875" customWidth="1"/>
+    <col min="3" max="3" width="15.75" customWidth="1"/>
+    <col min="4" max="5" width="12.625" customWidth="1"/>
+    <col min="6" max="6" width="12.375" customWidth="1"/>
+    <col min="7" max="7" width="14.75" customWidth="1"/>
+    <col min="8" max="8" width="15.75" customWidth="1"/>
+    <col min="9" max="9" width="13.5" customWidth="1"/>
+    <col min="11" max="11" width="17" customWidth="1"/>
+    <col min="14" max="14" width="14.5" customWidth="1"/>
+    <col min="15" max="16" width="15.875" customWidth="1"/>
+    <col min="29" max="29" width="14" customWidth="1"/>
+    <col min="30" max="30" width="22.125" customWidth="1"/>
+    <col min="33" max="33" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="18" customHeight="1" spans="1:33">

--- a/erp-server/erp-server-file/src/main/resources/excel/scm/purchaseOrderExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/scm/purchaseOrderExport.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="采购订单数据" sheetId="1" r:id="rId1"/>
@@ -27,11 +27,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t>采购单号</t>
   </si>
   <si>
+    <t>采购组织</t>
+  </si>
+  <si>
     <t>来源单号</t>
   </si>
   <si>
@@ -126,6 +129,9 @@
   </si>
   <si>
     <t>{.code}</t>
+  </si>
+  <si>
+    <t>{.purchaseOrgName}</t>
   </si>
   <si>
     <t>{.sourceCode}</t>
@@ -1421,25 +1427,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AF2"/>
+  <dimension ref="A1:AG2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
-    <col min="2" max="2" width="15.75" customWidth="1"/>
-    <col min="3" max="4" width="12.625" customWidth="1"/>
-    <col min="5" max="5" width="12.375" customWidth="1"/>
-    <col min="6" max="6" width="14.75" customWidth="1"/>
-    <col min="7" max="7" width="15.75" customWidth="1"/>
-    <col min="8" max="8" width="13.5" customWidth="1"/>
-    <col min="10" max="10" width="17" customWidth="1"/>
-    <col min="13" max="13" width="14.5" customWidth="1"/>
-    <col min="14" max="15" width="15.875" customWidth="1"/>
-    <col min="28" max="28" width="14" customWidth="1"/>
-    <col min="29" max="29" width="22.125" customWidth="1"/>
-    <col min="32" max="32" width="20" customWidth="1"/>
+    <col min="2" max="2" width="16.875" customWidth="1"/>
+    <col min="3" max="3" width="15.75" customWidth="1"/>
+    <col min="4" max="5" width="12.625" customWidth="1"/>
+    <col min="6" max="6" width="12.375" customWidth="1"/>
+    <col min="7" max="7" width="14.75" customWidth="1"/>
+    <col min="8" max="8" width="15.75" customWidth="1"/>
+    <col min="9" max="9" width="13.5" customWidth="1"/>
+    <col min="11" max="11" width="17" customWidth="1"/>
+    <col min="14" max="14" width="14.5" customWidth="1"/>
+    <col min="15" max="16" width="15.875" customWidth="1"/>
+    <col min="29" max="29" width="14" customWidth="1"/>
+    <col min="30" max="30" width="22.125" customWidth="1"/>
+    <col min="33" max="33" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="18" customHeight="1" spans="1:32">
+    <row r="1" s="1" customFormat="1" ht="18" customHeight="1" spans="1:33">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1536,103 +1543,109 @@
       <c r="AF1" s="2" t="s">
         <v>31</v>
       </c>
+      <c r="AG1" s="2" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="2" spans="1:32">
+    <row r="2" spans="1:33">
       <c r="A2" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="W2" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="X2" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Y2" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Z2" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AA2" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AC2" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD2" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AE2" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AF2" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="AG2" s="3" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
